--- a/data-raw/ces25_occupations.xlsx
+++ b/data-raw/ces25_occupations.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="14_{25EBDCBA-82E2-C04C-BA32-664A07F8A8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19940" xr2:uid="{55EBCFC0-9768-4FEA-8307-9AAA8801AB72}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19500" xr2:uid="{55EBCFC0-9768-4FEA-8307-9AAA8801AB72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4540,7 +4540,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
